--- a/examples/umroller/02_Stueckliste_UR-01.xlsx
+++ b/examples/umroller/02_Stueckliste_UR-01.xlsx
@@ -2040,7 +2040,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>/3.3</t>
+          <t>/9.1</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Klemmleiste Feldgeraete (Sensoren, Taster, Umrichter-Signale)</t>
+          <t>Klemmleiste Feldgeraete (Sensoren, Taster, Umrichter-Signale, Sicherheitskreise)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>/9.3</t>
+          <t>/7.2</t>
         </is>
       </c>
     </row>
